--- a/template/directory-template.xlsx
+++ b/template/directory-template.xlsx
@@ -522,21 +522,21 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Hindi: Committee</v>
+        <v>Theme</v>
       </c>
       <c r="B11" t="str">
-        <v>समिति</v>
+        <v>navy</v>
       </c>
       <c r="C11" t="str">
-        <v>हिंदी में अनुभाग का नाम</v>
+        <v>navy, forest, plum, slate, sunset, ocean, paper</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Hindi: Emergency</v>
+        <v>Hindi: Committee</v>
       </c>
       <c r="B12" t="str">
-        <v>आपातकालीन संपर्क</v>
+        <v>समिति</v>
       </c>
       <c r="C12" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Hindi: Services &amp; Help</v>
+        <v>Hindi: Emergency</v>
       </c>
       <c r="B13" t="str">
-        <v>सेवाएँ और सहायता</v>
+        <v>आपातकालीन संपर्क</v>
       </c>
       <c r="C13" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Hindi: Residents</v>
+        <v>Hindi: Services &amp; Help</v>
       </c>
       <c r="B14" t="str">
-        <v>निवासी</v>
+        <v>सेवाएँ और सहायता</v>
       </c>
       <c r="C14" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Hindi: Documents</v>
+        <v>Hindi: Residents</v>
       </c>
       <c r="B15" t="str">
-        <v>दस्तावेज़</v>
+        <v>निवासी</v>
       </c>
       <c r="C15" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -577,24 +577,24 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Note: Services &amp; Help</v>
+        <v>Hindi: Documents</v>
       </c>
       <c r="B16" t="str">
-        <v>These contacts are collected from fellow residents. The society has not verified or endorsed any of them. Please check credentials and agree charges before engaging anyone — you do so at your own risk.</v>
+        <v>दस्तावेज़</v>
       </c>
       <c r="C16" t="str">
-        <v>उस अनुभाग के नीचे दिखने वाली चेतावनी</v>
+        <v>हिंदी में अनुभाग का नाम</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Note HI: Services &amp; Help</v>
+        <v>Note: Services &amp; Help</v>
       </c>
       <c r="B17" t="str">
-        <v>ये संपर्क अन्य निवासियों द्वारा दिए गए हैं। सोसाइटी ने इनकी जाँच नहीं की है। काम शुरू कराने से पहले कृपया स्वयं पुष्टि करें और शुल्क तय कर लें — जोखिम आपका अपना होगा।</v>
+        <v>These contacts are collected from members. They have not been verified or endorsed. Please check credentials and agree charges before engaging anyone — you do so at your own risk.</v>
       </c>
       <c r="C17" t="str">
-        <v>वही चेतावनी हिंदी में</v>
+        <v>उस अनुभाग के नीचे दिखने वाली चेतावनी</v>
       </c>
     </row>
   </sheetData>

--- a/template/directory-template.xlsx
+++ b/template/directory-template.xlsx
@@ -9,7 +9,8 @@
     <sheet name="Services &amp; Help" sheetId="4" r:id="rId4"/>
     <sheet name="Residents" sheetId="5" r:id="rId5"/>
     <sheet name="Documents" sheetId="6" r:id="rId6"/>
-    <sheet name="_Read me" sheetId="7" r:id="rId7"/>
+    <sheet name="_Private" sheetId="7" r:id="rId7"/>
+    <sheet name="_Read me" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -841,7 +842,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:R3"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -849,9 +850,18 @@
     <col min="4" max="4" width="17.83203125" customWidth="1"/>
     <col min="5" max="5" width="19.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="17.83203125" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1"/>
-    <col min="9" max="9" width="23.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="32.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="16" max="16" width="17.83203125" customWidth="1"/>
+    <col min="17" max="17" width="17.83203125" customWidth="1"/>
+    <col min="18" max="18" width="23.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -874,12 +884,39 @@
         <v>Type</v>
       </c>
       <c r="G1" t="str">
+        <v>Blood Group</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Emergency Contact</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Vehicle No</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Vehicle Type</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Parking Slot</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Profession</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Language</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Occupants</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Pets</v>
+      </c>
+      <c r="P1" t="str">
         <v>Owner Name</v>
       </c>
-      <c r="H1" t="str">
+      <c r="Q1" t="str">
         <v>Owner Phone</v>
       </c>
-      <c r="I1" t="str">
+      <c r="R1" t="str">
         <v>Owner Address</v>
       </c>
     </row>
@@ -903,12 +940,39 @@
         <v>Owner</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>O+</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Relative name, +91 98220 11111</v>
       </c>
       <c r="I2" t="str">
+        <v>MH-09-AB-1234</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Car</v>
+      </c>
+      <c r="K2" t="str">
+        <v>P-12</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Doctor</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Marathi</v>
+      </c>
+      <c r="N2" t="str">
+        <v>4</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
         <v/>
       </c>
     </row>
@@ -932,18 +996,45 @@
         <v>Tenant</v>
       </c>
       <c r="G3" t="str">
+        <v>A+</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>MH-09-CD-5678</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Two-wheeler</v>
+      </c>
+      <c r="K3" t="str">
+        <v>P-31</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Hindi</v>
+      </c>
+      <c r="N3" t="str">
+        <v>2</v>
+      </c>
+      <c r="O3" t="str">
+        <v>1 cat</v>
+      </c>
+      <c r="P3" t="str">
         <v>Flat Owner Name</v>
       </c>
-      <c r="H3" t="str">
+      <c r="Q3" t="str">
         <v>+91 98200 44002</v>
       </c>
-      <c r="I3" t="str">
+      <c r="R3" t="str">
         <v>Owner's address, city</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1002,7 +1093,106 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:H3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="21.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Flat</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Person</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Relation</v>
+      </c>
+      <c r="D1" t="str">
+        <v>DOB</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Medical Notes</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Elderly or alone</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Lease Ends</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Police Verification</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>A-101</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Example Owner</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="D2" t="str">
+        <v>1979-04-12</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Diabetic</v>
+      </c>
+      <c r="F2" t="str">
+        <v>No</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>B-403</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Example Tenant</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="D3" t="str">
+        <v>1990-08-30</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>No</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2027-03-31</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Done 2026-02-10</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="70.83203125" customWidth="1"/>
@@ -1154,18 +1344,62 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>Blood group</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Shown as a red badge on the card. Use a dropdown in your form so you do not collect "o positive" and "O +ve".</v>
+      </c>
+      <c r="C14" t="str">
+        <v>कार्ड पर लाल बैज में दिखता है। फ़ॉर्म में ड्रॉपडाउन रखें।</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Optional fields</v>
+      </c>
+      <c r="B15" t="str">
+        <v>The first two extra columns show on the card; the rest fold behind a More details button. Search still finds them and opens the card.</v>
+      </c>
+      <c r="C15" t="str">
+        <v>पहले दो अतिरिक्त कॉलम कार्ड पर दिखते हैं, बाक़ी "More details" के पीछे। खोज उन्हें भी ढूँढ लेती है।</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Owner columns</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Fill Owner Name / Owner Phone / Owner Address only for tenanted flats. They appear behind an Owner details button; leave blank and nothing is shown.</v>
+      </c>
+      <c r="C16" t="str">
+        <v>किरायेदार वाले फ्लैट के लिए ही भरें। खाली छोड़ने पर कुछ नहीं दिखेगा।</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>_Private sheet</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Dates of birth, medical notes, lease dates and police verification live here. The leading underscore keeps the sheet off the website entirely.</v>
+      </c>
+      <c r="C17" t="str">
+        <v>जन्मतिथि, चिकित्सा जानकारी आदि यहाँ रखें। यह शीट वेबसाइट पर कभी नहीं दिखती।</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>Examples</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B18" t="str">
         <v>Delete the example rows before publishing.</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C18" t="str">
         <v>प्रकाशित करने से पहले उदाहरण पंक्तियाँ हटा दें।</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/template/directory-template.xlsx
+++ b/template/directory-template.xlsx
@@ -842,26 +842,27 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:S4"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="19.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="17.83203125" customWidth="1"/>
-    <col min="5" max="5" width="19.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="32.83203125" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="9" max="9" width="32.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" customWidth="1"/>
     <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
     <col min="13" max="13" width="12.83203125" customWidth="1"/>
     <col min="14" max="14" width="12.83203125" customWidth="1"/>
     <col min="15" max="15" width="12.83203125" customWidth="1"/>
-    <col min="16" max="16" width="17.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
     <col min="17" max="17" width="17.83203125" customWidth="1"/>
-    <col min="18" max="18" width="23.83203125" customWidth="1"/>
+    <col min="18" max="18" width="17.83203125" customWidth="1"/>
+    <col min="19" max="19" width="23.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -875,48 +876,51 @@
         <v>Flat</v>
       </c>
       <c r="D1" t="str">
+        <v>Unit Type</v>
+      </c>
+      <c r="E1" t="str">
         <v>Phone</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Email</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Type</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Blood Group</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Emergency Contact</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Vehicle No</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Vehicle Type</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Parking Slot</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Profession</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>Language</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Occupants</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>Pets</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>Owner Name</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>Owner Phone</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>Owner Address</v>
       </c>
     </row>
@@ -931,41 +935,41 @@
         <v>A-101</v>
       </c>
       <c r="D2" t="str">
+        <v>Flat</v>
+      </c>
+      <c r="E2" t="str">
         <v>+91 98330 40011</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>owner@example.com</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>Owner</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>O+</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>Relative name, +91 98220 11111</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>MH-09-AB-1234</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>Car</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>P-12</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>Doctor</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>Marathi</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>4</v>
       </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
       <c r="P2" t="str">
         <v/>
       </c>
@@ -973,6 +977,9 @@
         <v/>
       </c>
       <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
         <v/>
       </c>
     </row>
@@ -987,54 +994,116 @@
         <v>B-403</v>
       </c>
       <c r="D3" t="str">
+        <v>Flat</v>
+      </c>
+      <c r="E3" t="str">
         <v>+91 98330 40017</v>
       </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
         <v>Tenant</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>A+</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
       <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
         <v>MH-09-CD-5678</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>Two-wheeler</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>P-31</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>Teacher</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>Hindi</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>2</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <v>1 cat</v>
       </c>
-      <c r="P3" t="str">
+      <c r="Q3" t="str">
         <v>Flat Owner Name</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="R3" t="str">
         <v>+91 98200 44002</v>
       </c>
-      <c r="R3" t="str">
+      <c r="S3" t="str">
         <v>Owner's address, city</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Example Row House</v>
+      </c>
+      <c r="B4" t="str">
+        <v>B</v>
+      </c>
+      <c r="C4" t="str">
+        <v>B-11</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Row House</v>
+      </c>
+      <c r="E4" t="str">
+        <v>+91 98330 40021</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="H4" t="str">
+        <v>B+</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v>Marathi</v>
+      </c>
+      <c r="O4" t="str">
+        <v>5</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S4"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/template/directory-template.xlsx
+++ b/template/directory-template.xlsx
@@ -4,13 +4,14 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Committee" sheetId="2" r:id="rId2"/>
-    <sheet name="Emergency" sheetId="3" r:id="rId3"/>
-    <sheet name="Services &amp; Help" sheetId="4" r:id="rId4"/>
-    <sheet name="Residents" sheetId="5" r:id="rId5"/>
-    <sheet name="Documents" sheetId="6" r:id="rId6"/>
-    <sheet name="_Private" sheetId="7" r:id="rId7"/>
-    <sheet name="_Read me" sheetId="8" r:id="rId8"/>
+    <sheet name="Notices" sheetId="2" r:id="rId2"/>
+    <sheet name="Committee" sheetId="3" r:id="rId3"/>
+    <sheet name="Emergency" sheetId="4" r:id="rId4"/>
+    <sheet name="Services &amp; Help" sheetId="5" r:id="rId5"/>
+    <sheet name="Residents" sheetId="6" r:id="rId6"/>
+    <sheet name="Documents" sheetId="7" r:id="rId7"/>
+    <sheet name="_Private" sheetId="8" r:id="rId8"/>
+    <sheet name="_Read me" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -404,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="62.83203125" customWidth="1"/>
@@ -534,10 +535,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Hindi: Committee</v>
+        <v>Hindi: Notices</v>
       </c>
       <c r="B12" t="str">
-        <v>समिति</v>
+        <v>सूचनाएँ</v>
       </c>
       <c r="C12" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -545,10 +546,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Hindi: Emergency</v>
+        <v>Hindi: Committee</v>
       </c>
       <c r="B13" t="str">
-        <v>आपातकालीन संपर्क</v>
+        <v>समिति</v>
       </c>
       <c r="C13" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -556,10 +557,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Hindi: Services &amp; Help</v>
+        <v>Hindi: Emergency</v>
       </c>
       <c r="B14" t="str">
-        <v>सेवाएँ और सहायता</v>
+        <v>आपातकालीन संपर्क</v>
       </c>
       <c r="C14" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -567,10 +568,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Hindi: Residents</v>
+        <v>Hindi: Services &amp; Help</v>
       </c>
       <c r="B15" t="str">
-        <v>निवासी</v>
+        <v>सेवाएँ और सहायता</v>
       </c>
       <c r="C15" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -578,10 +579,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Hindi: Documents</v>
+        <v>Hindi: Residents</v>
       </c>
       <c r="B16" t="str">
-        <v>दस्तावेज़</v>
+        <v>निवासी</v>
       </c>
       <c r="C16" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -589,23 +590,134 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
+        <v>Hindi: Documents</v>
+      </c>
+      <c r="B17" t="str">
+        <v>दस्तावेज़</v>
+      </c>
+      <c r="C17" t="str">
+        <v>हिंदी में अनुभाग का नाम</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>Note: Services &amp; Help</v>
       </c>
-      <c r="B17" t="str">
+      <c r="B18" t="str">
         <v>These contacts are collected from members. They have not been verified or endorsed. Please check credentials and agree charges before engaging anyone — you do so at your own risk.</v>
       </c>
-      <c r="C17" t="str">
+      <c r="C18" t="str">
         <v>उस अनुभाग के नीचे दिखने वाली चेतावनी</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="49.83203125" customWidth="1"/>
+    <col min="3" max="3" width="150.83203125" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Details</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Pinned</v>
+      </c>
+      <c r="F1" t="str">
+        <v>File</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Maintenance for this quarter is due</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Kindly pay by the 15th. Bank and UPI details are with the treasurer.</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Payment</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Annual General Meeting — Sunday 20 April, 10 AM</v>
+      </c>
+      <c r="C3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Agenda: audited accounts, maintenance revision, and election of the new committee.
+If you cannot attend, send your written consent with a neighbour.</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Meeting</v>
+      </c>
+      <c r="E3" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Water tank cleaning — Thursday 3 April</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Supply will be off between 9 AM and 2 PM. Please store what you need.</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Maintenance</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
   <cols>
@@ -674,7 +786,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D5"/>
   <cols>
@@ -761,7 +873,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <cols>
@@ -840,7 +952,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:S4"/>
   <cols>
@@ -1108,7 +1220,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <cols>
@@ -1160,7 +1272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
   <cols>
@@ -1259,7 +1371,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>

--- a/template/directory-template.xlsx
+++ b/template/directory-template.xlsx
@@ -875,14 +875,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="23.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -893,15 +894,18 @@
         <v>Role</v>
       </c>
       <c r="C1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="D1" t="str">
         <v>Charges</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Timings</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Phone</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -913,15 +917,18 @@
         <v>Plumber</v>
       </c>
       <c r="C2" t="str">
+        <v>Repairs &amp; Maintenance</v>
+      </c>
+      <c r="D2" t="str">
         <v>₹100 / visit</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>9 AM – 7 PM</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>+91 90040 55511</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>Parts charged separately</v>
       </c>
     </row>
@@ -933,21 +940,24 @@
         <v>Maid</v>
       </c>
       <c r="C3" t="str">
+        <v>Home Help</v>
+      </c>
+      <c r="D3" t="str">
         <v>₹50 / visit</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>7 AM – 11 AM</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>+91 90210 33001</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>झाड़ू, पोछा, बर्तन</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
   </ignoredErrors>
 </worksheet>
 </file>
